--- a/output/reports/cv_experiment_SVM_qcut_regression.xlsx
+++ b/output/reports/cv_experiment_SVM_qcut_regression.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -491,23 +491,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32633185386658</v>
+        <v>1.295900821685791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998932697326653</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99994714155579</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G2" t="n">
-        <v>1.29374818976295</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6823112120831791</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -526,93 +526,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>38.44898915290833</v>
+        <v>1.534951448440552</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999198365548818</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99994714155579</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G3" t="n">
-        <v>1.29374818976295</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6823112120831791</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>74.73320746421814</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999343494990329</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.99994714155579</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.29374818976295</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6823112120831791</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>112.6018803119659</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999384639869466</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.99994714155579</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.29374818976295</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.6823112120831791</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -627,7 +557,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,23 +622,23 @@
         <v>3</v>
       </c>
       <c r="D2" t="n">
-        <v>26.32633185386658</v>
+        <v>1.295900821685791</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9998932697326653</v>
+        <v>0.9907215425595718</v>
       </c>
       <c r="F2" t="n">
-        <v>0.99994714155579</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G2" t="n">
-        <v>1.29374818976295</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H2" t="n">
-        <v>0.6823112120831791</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
         </is>
       </c>
     </row>
@@ -727,93 +657,23 @@
         <v>5</v>
       </c>
       <c r="D3" t="n">
-        <v>38.44898915290833</v>
+        <v>1.534951448440552</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9999198365548818</v>
+        <v>0.994952709138001</v>
       </c>
       <c r="F3" t="n">
-        <v>0.99994714155579</v>
+        <v>0.9938816684425166</v>
       </c>
       <c r="G3" t="n">
-        <v>1.29374818976295</v>
+        <v>1.541436429431279</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6823112120831791</v>
+        <v>0.9433131263880609</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C4" t="n">
-        <v>10</v>
-      </c>
-      <c r="D4" t="n">
-        <v>74.73320746421814</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.9999343494990329</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.99994714155579</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1.29374818976295</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.6823112120831791</v>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>SVM</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>15</v>
-      </c>
-      <c r="D5" t="n">
-        <v>112.6018803119659</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9999384639869466</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.99994714155579</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1.29374818976295</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.6823112120831791</v>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>{'kernel': 'rbf', 'gamma': 'scale', 'epsilon': 0.01, 'C': 500}</t>
+          <t>{'kernel': 'rbf', 'gamma': 'auto', 'epsilon': 0.01, 'C': 500}</t>
         </is>
       </c>
     </row>
